--- a/hira_material_automation/output/monthly/202601_202610__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__temporary_synovial_substitute__250099__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:01</t>
+          <t>2026-10-14T23:46:34</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>96e4de10f03aeeac0323770dd30f24cc36c243604d058df759e41301ba8d485f</t>
+          <t>cb80a2c5e768be0c60080b53941745ac3d8b596d0614535af18d0f6e60b6a008</t>
         </is>
       </c>
     </row>
